--- a/Documentation/PCB BOMs.xlsx
+++ b/Documentation/PCB BOMs.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Arcade-Project\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Arcade-Project\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DBC70E-18A6-4BA2-9ECA-4918AF92645A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PCB-AuxControl" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="128">
   <si>
     <t>Qty</t>
   </si>
@@ -395,13 +396,22 @@
   </si>
   <si>
     <t>ST POWER PCB BOM 12/27/2021</t>
+  </si>
+  <si>
+    <t>Teensy 3.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Teensy 3.2 is End of Life, it has been replaced by the Teensy 4.0 (Drop in ) </t>
+  </si>
+  <si>
+    <t>https://www.pjrc.com/store/teensy40.html</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -542,8 +552,16 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -723,8 +741,20 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -865,8 +895,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -909,26 +950,23 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="42" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -962,6 +1000,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1247,8 +1286,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F79"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
@@ -1257,19 +1296,20 @@
     <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="52.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="71.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-    </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1289,7 +1329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>4</v>
       </c>
@@ -1305,7 +1345,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>5</v>
       </c>
@@ -1321,7 +1361,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1337,7 +1377,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -1355,7 +1395,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -1373,7 +1413,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -1391,7 +1431,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -1407,7 +1447,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1</v>
       </c>
@@ -1422,129 +1462,135 @@
       <c r="F10" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="G10" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>1</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="B14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F14" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>1</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>1</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7" t="s">
+      <c r="D15" s="3"/>
+      <c r="E15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F15" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>1</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7" t="s">
+      <c r="D16" s="3"/>
+      <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F16" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>2</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7" t="s">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7" t="s">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>4</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1553,14 +1599,14 @@
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1569,14 +1615,14 @@
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="5" t="s">
-        <v>69</v>
+      <c r="E22" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1585,60 +1631,60 @@
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>4</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3" t="s">
+      <c r="D24" s="3"/>
+      <c r="E24" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="B27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>2</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1647,11 +1693,11 @@
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>14</v>
@@ -1659,15 +1705,15 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>14</v>
@@ -1675,15 +1721,15 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>14</v>
@@ -1695,295 +1741,293 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
+        <v>1</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
         <v>6</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
-        <v>1</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>1</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>1</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
-        <v>1</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D36" s="3"/>
-      <c r="E36" s="3" t="s">
-        <v>56</v>
+      <c r="E36" t="s">
+        <v>67</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>1</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F38" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="G38" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="9">
+        <v>1</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="4"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="B42" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E42" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F42" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
-        <v>1</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>1</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3" t="s">
+      <c r="D43" s="3"/>
+      <c r="E43" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F43" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
-        <v>1</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>1</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3" t="s">
+      <c r="D44" s="3"/>
+      <c r="E44" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F44" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <v>1</v>
-      </c>
-      <c r="B43" s="3" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>1</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
         <v>2</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B46" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F46" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
         <v>7</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B47" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
-        <v>1</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
-        <v>1</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>1</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>42</v>
@@ -1992,295 +2036,297 @@
         <v>38</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
+        <v>1</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>1</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
         <v>2</v>
-      </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
-        <v>1</v>
-      </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
-        <v>1</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="3" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>19</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
+      <c r="E54" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="F54" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="D55" s="3"/>
-      <c r="E55" s="5" t="s">
-        <v>67</v>
+      <c r="E55" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="D56" s="3"/>
-      <c r="E56" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>1</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" t="s">
+        <v>67</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <v>2</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <v>1</v>
+      </c>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3" t="s">
+      <c r="D59" s="3"/>
+      <c r="E59" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F59" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="11"/>
-      <c r="B58" s="10"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="G59" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="9">
+        <v>1</v>
+      </c>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="B63" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D63" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E63" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F63" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="3">
-        <v>1</v>
-      </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3" t="s">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <v>1</v>
+      </c>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3" t="s">
+      <c r="D64" s="3"/>
+      <c r="E64" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="F64" s="3" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="3">
-        <v>2</v>
-      </c>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="3">
-        <v>7</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="3">
-        <v>2</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <v>1</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>81</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B65" s="3"/>
       <c r="C65" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>38</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="D65" s="3"/>
       <c r="E65" s="3" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>49</v>
@@ -2288,106 +2334,112 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>1</v>
-      </c>
-      <c r="B67" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="C67" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
+        <v>1</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
+        <v>1</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
+        <v>1</v>
+      </c>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3" t="s">
+      <c r="D70" s="3"/>
+      <c r="E70" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F70" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="11"/>
-      <c r="B68" s="10"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="8" t="s">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C70" s="2" t="s">
+      <c r="B73" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
-        <v>1</v>
-      </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
-        <v>1</v>
-      </c>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="3">
-        <v>1</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2396,16 +2448,14 @@
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>110</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D74" s="3"/>
       <c r="E74" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2414,33 +2464,33 @@
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="3" t="s">
-        <v>113</v>
+        <v>8</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>113</v>
+        <v>12</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>2</v>
-      </c>
-      <c r="B76" s="3">
-        <v>330</v>
+        <v>1</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>49</v>
@@ -2452,69 +2502,130 @@
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3" t="s">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D78" s="3">
-        <v>1206</v>
+        <v>113</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>2</v>
       </c>
-      <c r="B79" s="3"/>
+      <c r="B79" s="3">
+        <v>330</v>
+      </c>
       <c r="C79" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <v>1</v>
+      </c>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
+        <v>2</v>
+      </c>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D81" s="3">
+        <v>1206</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
+        <v>2</v>
+      </c>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3" t="s">
+      <c r="D82" s="3"/>
+      <c r="E82" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F82" s="3" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A41:F41"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G60" r:id="rId1" xr:uid="{96AB444D-4FEB-4D4D-B557-8C74BD181C9D}"/>
+    <hyperlink ref="G39" r:id="rId2" xr:uid="{A21CC9F5-90E2-4343-B6F2-9E6F20C9519A}"/>
+    <hyperlink ref="G11" r:id="rId3" xr:uid="{50120836-3726-47FC-A764-42FE50AC60D2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="H20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
